--- a/docs/测试执行报告.xlsx
+++ b/docs/测试执行报告.xlsx
@@ -4903,12 +4903,12 @@
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>未执行</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>删除关联数据校验待专项验证</t>
+          <t>SQL 核验：删除后 sys_user_role / sys_user_post 关联记录已同步清理</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>91.6%</t>
         </is>
       </c>
     </row>
@@ -5667,10 +5667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>

--- a/docs/测试执行报告.xlsx
+++ b/docs/测试执行报告.xlsx
@@ -586,12 +586,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>验证码开关已关闭，无法执行</t>
+          <t>实测：开启验证码开关后提交错误验证码，接口返回"验证码错误"，登录被拦截</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>验证码开关已关闭，无法执行</t>
+          <t>实测：验证码留空提交，接口返回"验证码错误"（前端另有"请输入验证码"客户端校验），登录被拦截</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>验证码开关已关闭，无法执行</t>
+          <t>实测：获取验证码后等待 120 秒（Redis TTL 归零），提交后返回"验证码已失效"</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>需Firefox手工执行</t>
+          <t>Firefox 157 + geckodriver 0.37.1 实测：登录成功、用户管理列表渲染 10 行（截图见 screenshots/兼容性/）</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>需Edge手工执行</t>
+          <t>Edge 154 实测：登录成功、用户管理列表渲染 10 行（截图见 screenshots/兼容性/）</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4570,12 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>阻塞</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>需切换分辨率手工执行</t>
+          <t>Edge 实测 1366×768 与 1920×1080：无横向溢出、侧栏与表格正常（截图见 screenshots/兼容性/）</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
     </row>
